--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/TEST.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/TEST.xlsx
@@ -847,7 +847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.4140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.6640625" customWidth="1" style="6" min="1" max="1"/>

--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/TEST.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/TEST.xlsx
@@ -173,476 +173,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>76200</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <ext cx="1400175" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="image1.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>85725</colOff>
-      <row>4</row>
-      <rowOff>1247775</rowOff>
-    </from>
-    <ext cx="1457325" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="image2.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>47625</colOff>
-      <row>5</row>
-      <rowOff>1504950</rowOff>
-    </from>
-    <ext cx="1628775" cy="1724025"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="image3.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>57150</colOff>
-      <row>6</row>
-      <rowOff>1524000</rowOff>
-    </from>
-    <ext cx="1609725" cy="1743075"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="image4.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>57150</colOff>
-      <row>7</row>
-      <rowOff>1638300</rowOff>
-    </from>
-    <ext cx="1676400" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="image5.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>1895475</colOff>
-      <row>9</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <ext cx="1924050" cy="1476375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="image6.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>190500</colOff>
-      <row>9</row>
-      <rowOff>1638300</rowOff>
-    </from>
-    <ext cx="1952625" cy="1628775"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="image7.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>180975</colOff>
-      <row>10</row>
-      <rowOff>1533525</rowOff>
-    </from>
-    <ext cx="2019300" cy="1847850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="image8.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>38100</colOff>
-      <row>13</row>
-      <rowOff>1638300</rowOff>
-    </from>
-    <ext cx="2047875" cy="1695450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="image9.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>57150</colOff>
-      <row>11</row>
-      <rowOff>1790700</rowOff>
-    </from>
-    <ext cx="1924050" cy="1724025"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="image10.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>57150</colOff>
-      <row>14</row>
-      <rowOff>1619250</rowOff>
-    </from>
-    <ext cx="1924050" cy="1819275"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="image11.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>47625</colOff>
-      <row>16</row>
-      <rowOff>57150</rowOff>
-    </from>
-    <ext cx="2000250" cy="1933575"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="image12.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>38100</colOff>
-      <row>16</row>
-      <rowOff>2133600</rowOff>
-    </from>
-    <ext cx="2000250" cy="1743075"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="image13.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>57150</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1924050" cy="1581150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="image14.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>38100</colOff>
-      <row>12</row>
-      <rowOff>1781175</rowOff>
-    </from>
-    <ext cx="2009775" cy="1514475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="image15.jpg"/>
-        <cNvPicPr preferRelativeResize="0"/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData fLocksWithSheet="0"/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
